--- a/data/trans_orig/IP07C07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C07-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2007 (tasa de respuesta: 88,89%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2007 (tasa de respuesta: 88,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19388</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16430</t>
+          <t>16289</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,81%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19189</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>7613</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17142</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19402</t>
+          <t>19195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19638</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33526</t>
+          <t>33096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28976</t>
+          <t>29260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>27338</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39033</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49112</t>
+          <t>49618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63968</t>
+          <t>64674</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9053</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18987</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26937</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33566</t>
+          <t>33949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44471</t>
+          <t>43810</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>81,1%</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>15511</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>23363</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13558</t>
+          <t>13661</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>13157</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24045</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12199</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21330</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>23050</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>35034</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>19328</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29853</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>70,13%</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16281</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>21355</t>
+          <t>21318</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>18445</t>
+          <t>18281</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>27222</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>37951</t>
+          <t>38178</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,26%</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>12915</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>23634</t>
+          <t>22733</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>30096</t>
+          <t>29764</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>40522</t>
+          <t>40572</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>33404</t>
+          <t>33488</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>43627</t>
+          <t>43875</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>66819</t>
+          <t>67333</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>81387</t>
+          <t>81292</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>10341</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>13565</t>
+          <t>13553</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>26270</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>25361</t>
+          <t>25271</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>29754</t>
+          <t>30042</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>46662</t>
+          <t>45952</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>22872</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>21400</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>24035</t>
+          <t>24596</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>40956</t>
+          <t>40635</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>22993</t>
+          <t>23687</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>36345</t>
+          <t>36928</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>25929</t>
+          <t>25468</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>38907</t>
+          <t>38753</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>52637</t>
+          <t>51759</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>72302</t>
+          <t>71366</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>41491</t>
+          <t>42176</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>62665</t>
+          <t>63703</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>50845</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>73831</t>
+          <t>74238</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>99030</t>
+          <t>99722</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>129499</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>55687</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>77911</t>
+          <t>78536</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>55303</t>
+          <t>55157</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>78170</t>
+          <t>77124</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>116689</t>
+          <t>116514</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>148889</t>
+          <t>149897</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>146177</t>
+          <t>146234</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>174200</t>
+          <t>174610</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>155819</t>
+          <t>155494</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>184475</t>
+          <t>182999</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>311585</t>
+          <t>309451</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>348669</t>
+          <t>348953</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,75%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>14245</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21109</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16349</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>24251</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>26527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38391</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,78%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>16856</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>10039</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22631</t>
+          <t>22084</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>11599</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>20859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>20173</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31438</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32559</t>
+          <t>32771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>43150</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55492</t>
+          <t>56109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71420</t>
+          <t>71016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>17462</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>21698</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23819</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35952</t>
+          <t>35793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,46%</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9157,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>637</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>14387</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31244</t>
+          <t>30918</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,37%</t>
         </is>
       </c>
     </row>
@@ -9491,12 +9491,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16966</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9526,12 +9526,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>732</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21189</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -9604,12 +9604,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18976</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>19878</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34489</t>
+          <t>34619</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>11951</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14613</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24585</t>
+          <t>24541</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,2%</t>
         </is>
       </c>
     </row>
@@ -10173,12 +10173,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10188,12 +10188,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -10286,12 +10286,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10301,12 +10301,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11018</t>
+          <t>10762</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>21389</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10901</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>735</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -10855,12 +10855,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13707</t>
+          <t>13989</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10940,12 +10940,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -10968,12 +10968,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>20978</t>
+          <t>20775</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21116</t>
+          <t>21123</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11018,12 +11018,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>29491</t>
+          <t>29062</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>40366</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,59%</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17479</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11043</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>22039</t>
+          <t>21664</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>20330</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>35054</t>
+          <t>35665</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -11537,12 +11537,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>17932</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11587,12 +11587,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>16026</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>29798</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -11650,12 +11650,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>23157</t>
+          <t>22979</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>34628</t>
+          <t>35128</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>17149</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>29579</t>
+          <t>29016</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>43299</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>60442</t>
+          <t>60570</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11735,12 +11735,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,82 +11895,82 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>4575</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>7359</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>4685</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>7602</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>26098</t>
+          <t>26061</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>25283</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -12219,12 +12219,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>14016</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>26390</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>27988</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>32847</t>
+          <t>32587</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>50261</t>
+          <t>50240</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -12332,12 +12332,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>30213</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>43923</t>
+          <t>44321</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24556</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>37674</t>
+          <t>38011</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>57971</t>
+          <t>57860</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>78381</t>
+          <t>78517</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>18063</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>31168</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>58064</t>
+          <t>58491</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>82404</t>
+          <t>82407</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>71698</t>
+          <t>70082</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>99194</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>136530</t>
+          <t>135655</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>171172</t>
+          <t>170443</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>58684</t>
+          <t>59393</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>81668</t>
+          <t>82888</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>62822</t>
+          <t>64009</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>107808</t>
+          <t>108704</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>139970</t>
+          <t>140572</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>137310</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>167613</t>
+          <t>166502</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>158383</t>
+          <t>156454</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>185947</t>
+          <t>187922</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>304901</t>
+          <t>303096</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>343086</t>
+          <t>345763</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13520,7 +13520,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17530</t>
+          <t>17619</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -13819,12 +13819,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13834,12 +13834,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12370</t>
+          <t>12523</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -13932,12 +13932,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13967,12 +13967,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14002,12 +14002,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30044</t>
+          <t>29865</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14017,12 +14017,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,61%</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -14280,7 +14280,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14350,7 +14350,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -14501,12 +14501,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>17183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14516,12 +14516,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14536,12 +14536,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14551,12 +14551,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22823</t>
+          <t>23215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14586,12 +14586,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -14614,12 +14614,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33653</t>
+          <t>33086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43940</t>
+          <t>43743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14649,12 +14649,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41971</t>
+          <t>42457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51506</t>
+          <t>51457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14684,12 +14684,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79414</t>
+          <t>79163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93375</t>
+          <t>93198</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -14962,7 +14962,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -15070,12 +15070,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15085,12 +15085,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>11066</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -15183,12 +15183,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15198,12 +15198,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15218,12 +15218,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15233,12 +15233,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15253,12 +15253,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19168</t>
+          <t>20551</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15268,12 +15268,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -15296,12 +15296,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19576</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>29290</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15311,12 +15311,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15331,12 +15331,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>17251</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26072</t>
+          <t>26305</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15346,12 +15346,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39976</t>
+          <t>39726</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53308</t>
+          <t>53315</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15381,12 +15381,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>12830</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>11052</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24081</t>
+          <t>24039</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15900,12 +15900,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15915,12 +15915,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15935,12 +15935,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10125</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15950,12 +15950,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -15978,12 +15978,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23054</t>
+          <t>23290</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15993,12 +15993,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>27178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16028,12 +16028,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33894</t>
+          <t>34249</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47786</t>
+          <t>47865</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16063,12 +16063,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -16213,7 +16213,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16283,7 +16283,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16361,7 +16361,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -16547,12 +16547,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>12252</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16562,12 +16562,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16582,12 +16582,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>17815</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>26972</t>
+          <t>27099</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16632,12 +16632,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,65%</t>
         </is>
       </c>
     </row>
@@ -16660,12 +16660,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16675,12 +16675,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16695,12 +16695,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10515</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16710,12 +16710,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17395</t>
+          <t>17369</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16745,12 +16745,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -16895,7 +16895,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17093,7 +17093,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -17116,12 +17116,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>13980</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17131,12 +17131,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12882</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17166,12 +17166,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>24340</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17264,12 +17264,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17279,12 +17279,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17299,12 +17299,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>23164</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17314,12 +17314,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -17342,12 +17342,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>17720</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17377,12 +17377,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>17427</t>
+          <t>17456</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>19003</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>31956</t>
+          <t>31943</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17427,12 +17427,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17690,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17775,7 +17775,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>13554</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>25709</t>
+          <t>25555</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>25666</t>
+          <t>25407</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>29207</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>46150</t>
+          <t>46631</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -17911,12 +17911,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17926,12 +17926,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17946,12 +17946,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>12522</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>25389</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17961,12 +17961,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17981,12 +17981,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>25674</t>
+          <t>25850</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>42757</t>
+          <t>42595</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17996,12 +17996,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>24460</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>37807</t>
+          <t>38498</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18039,12 +18039,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18059,12 +18059,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19526</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>32624</t>
+          <t>32716</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -18074,12 +18074,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -18094,12 +18094,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>48090</t>
+          <t>48374</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>67527</t>
+          <t>66460</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18109,12 +18109,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,56%</t>
         </is>
       </c>
     </row>
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>16095</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>25065</t>
+          <t>24329</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>28105</t>
+          <t>29199</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>24915</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>31418</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>49347</t>
+          <t>49022</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -18593,12 +18593,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>22613</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>36318</t>
+          <t>35767</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18628,12 +18628,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>25777</t>
+          <t>26011</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>39837</t>
+          <t>39770</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18643,12 +18643,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18663,12 +18663,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>51475</t>
+          <t>51184</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>71605</t>
+          <t>71592</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18678,12 +18678,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,24%</t>
         </is>
       </c>
     </row>
@@ -18706,12 +18706,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>21929</t>
+          <t>22150</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>25153</t>
+          <t>24656</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18756,12 +18756,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18776,12 +18776,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>26568</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>42978</t>
+          <t>42830</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18791,12 +18791,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>27397</t>
+          <t>26829</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>43601</t>
+          <t>42683</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>62023</t>
+          <t>63153</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>87938</t>
+          <t>88554</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>55151</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>80328</t>
+          <t>81339</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>125396</t>
+          <t>124252</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>162309</t>
+          <t>158861</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>71727</t>
+          <t>70901</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>98993</t>
+          <t>97946</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>83930</t>
+          <t>82862</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>111504</t>
+          <t>111134</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>160324</t>
+          <t>161242</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>202573</t>
+          <t>203389</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>143463</t>
+          <t>142682</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>174969</t>
+          <t>173522</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19403,12 +19403,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>151372</t>
+          <t>151390</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>182659</t>
+          <t>182720</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>305095</t>
+          <t>307525</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>351863</t>
+          <t>352295</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
